--- a/XBRL-template-MPERS/Group/14-Notes-IssuedCapital.xlsx
+++ b/XBRL-template-MPERS/Group/14-Notes-IssuedCapital.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -466,313 +466,243 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on issued capital [abstract]</t>
+          <t>Disclosure on issued capital</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Disclosure of issued capital [text block]</t>
+          <t>Disclosure of issued capital</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Issued Capital [abstract]</t>
+          <t>Issued Capital</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Disclosure of classes of share capital [table]</t>
+          <t>Issued capital</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Number of shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Number of shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classes of share capital [axis]</t>
+          <t>Other changes in number of shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share capital [member]</t>
+          <t>Amount of shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ordinary shares [member]</t>
+          <t>Balance at the beginning of period</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Redeemable preference shares [member]</t>
+          <t>Amount of shares issued for cash under ESOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Non-redeemable preference shares [member]</t>
+          <t>Amount of shares issued for cash under private placement</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Disclosure of classes of share capital [line items]</t>
+          <t>Amount of shares arising from conversion of ICULS by surrender option</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Issued capital [abstract]</t>
+          <t>Amount of shares arising from conversion of ICULS by mandatory conversion</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shares issued and fully paid [abstract]</t>
+          <t>Total amount of shares issued during financial year</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Number of shares issued and fully paid [abstract]</t>
+          <t>Other changes in amount of shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Number of shares issued and fully paid</t>
+          <t>Balance at the end of period</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other changes in number of shares issued and fully paid</t>
+          <t>Shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amount of shares issued and fully paid [abstract]</t>
+          <t>Number of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Balance at the beginning of period</t>
+          <t>Number of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amount of shares issued for cash under ESOS</t>
+          <t>Other changes in number of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amount of shares issued for cash under private placement</t>
+          <t>Amount of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amount of shares arising from conversion of ICULS by surrender option</t>
+          <t>Amount of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amount of shares arising from conversion of ICULS by mandatory conversion</t>
+          <t>Other changes in amount of shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Total amount of shares issued during financial year</t>
+          <t>Shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Other changes in amount of shares issued and fully paid</t>
+          <t>Number of shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Balance at the end of period</t>
+          <t>Number of shares outstanding at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shares issued but not fully paid [abstract]</t>
+          <t>Number of outstanding shares issued during financial year</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Number of shares issued but not fully paid [abstract]</t>
+          <t>Other changes in number of shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Number of shares issued but not fully paid</t>
+          <t>Number of shares outstanding at end of period</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other changes in number of shares issued but not fully paid</t>
+          <t>Amount of shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amount of shares issued but not fully paid [abstract]</t>
+          <t>Amount of shares outstanding at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amount of shares issued but not fully paid</t>
+          <t>Amount of outstanding shares issued during financial year</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Other changes in amount of shares issued but not fully paid</t>
+          <t>Other changes in amount of shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
-        <is>
-          <t>Shares outstanding [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding at beginning of period</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Number of outstanding shares issued during financial year</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Other changes in number of shares outstanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding at end of period</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Amount of shares outstanding [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Amount of shares outstanding at beginning of period</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Amount of outstanding shares issued during financial year</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Other changes in amount of shares outstanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
         <is>
           <t>Amount of shares outstanding at end of period</t>
         </is>

--- a/XBRL-template-MPERS/Group/14-Notes-IssuedCapital.xlsx
+++ b/XBRL-template-MPERS/Group/14-Notes-IssuedCapital.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +475,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on issued capital</t>
         </is>
@@ -478,28 +489,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Issued Capital</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Issued capital</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Shares issued and fully paid</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Number of shares issued and fully paid</t>
         </is>
@@ -520,7 +531,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Amount of shares issued and fully paid</t>
         </is>
@@ -583,14 +594,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Shares issued but not fully paid</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Number of shares issued but not fully paid</t>
         </is>
@@ -611,7 +622,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Amount of shares issued but not fully paid</t>
         </is>
@@ -632,14 +643,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Shares outstanding</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Number of shares outstanding</t>
         </is>
@@ -674,7 +685,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Amount of shares outstanding</t>
         </is>
